--- a/hardware/RCKid2-bom.xlsx
+++ b/hardware/RCKid2-bom.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_RCKid_RCKid_2023-11-01" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_RCKid_RCKid_2024-03-09" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="325">
   <si>
     <t>No.</t>
   </si>
@@ -46,58 +46,295 @@
     <t>1</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>SKRRACE010</t>
+  </si>
+  <si>
+    <t>A1,B1,B2,B3,BOTTOM1,LEFT1,RIGHT1,TOP1</t>
+  </si>
+  <si>
+    <t>KEY-SMD_4P-L7.5-W7.0-P5.00-TL</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ALPSALPINE(阿尔卑斯阿尔派)</t>
+  </si>
+  <si>
+    <t>C139798</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PJ-3420-A-SMT</t>
+  </si>
+  <si>
+    <t>AUDIO1</t>
+  </si>
+  <si>
+    <t>AUDIO-SMD_PJ-3420-A-SMT_C319102</t>
+  </si>
+  <si>
+    <t>XKBConnectivity(中国星坤)</t>
+  </si>
+  <si>
+    <t>C319102</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>HDR-M_2.54_1x1P</t>
+  </si>
+  <si>
+    <t>B+,B-</t>
+  </si>
+  <si>
+    <t>HDR-TH_1P-V-M_XKB_X4611WV-01I-C28D40</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>C66,C67,C136,C137</t>
+  </si>
+  <si>
+    <t>C0805</t>
+  </si>
+  <si>
+    <t>CL21A476MQYNNNE</t>
+  </si>
+  <si>
+    <t>SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>C16780</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>220pF</t>
+  </si>
+  <si>
+    <t>C70,C71</t>
+  </si>
+  <si>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>0402B221K500NT</t>
+  </si>
+  <si>
+    <t>FH(风华)</t>
+  </si>
+  <si>
+    <t>C1530</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>SKRRACE010</t>
-  </si>
-  <si>
-    <t>A1,B1,BOTTOM1,LEFT1,RIGHT1,TOP1</t>
-  </si>
-  <si>
-    <t>KEY-SMD_4P-L7.5-W7.0-P5.00-TL</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>ALPSALPINE(阿尔卑斯阿尔派)</t>
-  </si>
-  <si>
-    <t>C139798</t>
-  </si>
-  <si>
-    <t>LCSC</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PJ-3420-A-SMT</t>
-  </si>
-  <si>
-    <t>AUDIO1,AUDIO2</t>
-  </si>
-  <si>
-    <t>AUDIO-SMD_PJ-3420-A-SMT_C319102</t>
-  </si>
-  <si>
-    <t>XKBConnectivity(中国星坤)</t>
-  </si>
-  <si>
-    <t>C319102</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C74,C80</t>
+  </si>
+  <si>
+    <t>CL05A106MQ5NUNC</t>
+  </si>
+  <si>
+    <t>C15525</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C77,C115,C116,C121,C122,C123,C130,C131</t>
+  </si>
+  <si>
+    <t>CL05A105KA5NQNC</t>
+  </si>
+  <si>
+    <t>C52923</t>
+  </si>
+  <si>
+    <t>C81,C82</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>CL10A106MA8NRNC</t>
+  </si>
+  <si>
+    <t>C96446</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2.2uF</t>
+  </si>
+  <si>
+    <t>C83</t>
+  </si>
+  <si>
+    <t>CL10A225KO8NNNC</t>
+  </si>
+  <si>
+    <t>C23630</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C92,C95,C96,C101,C102,C103,C104,C107,C108,C109,C110,C111,C112,C113,C114,C117,C118,C124,C125,C126,C129,C142,C143,C144</t>
+  </si>
+  <si>
+    <t>CL05B104KB54PNC</t>
+  </si>
+  <si>
+    <t>C307331</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>33pF</t>
+  </si>
+  <si>
+    <t>C105,C106</t>
+  </si>
+  <si>
+    <t>0402CG330J500NT</t>
+  </si>
+  <si>
+    <t>C1562</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>C132,C151,C152</t>
+  </si>
+  <si>
+    <t>CL10A226MQ8NRNC</t>
+  </si>
+  <si>
+    <t>C59461</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>C138</t>
+  </si>
+  <si>
+    <t>CL05A475MP5NRNC</t>
+  </si>
+  <si>
+    <t>C23733</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>C145,C146,C147,C148,C149,C150</t>
+  </si>
+  <si>
+    <t>CL10A106KP8NNNC</t>
+  </si>
+  <si>
+    <t>C19702</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>1N5819WS</t>
+  </si>
+  <si>
+    <t>D4,D5,D6,D7,D8,D9,D10,D11,D12,D14,D15</t>
+  </si>
+  <si>
+    <t>SOD-323_L1.8-W1.3-LS2.5-RD</t>
+  </si>
+  <si>
+    <t>Hottech(合科泰)</t>
+  </si>
+  <si>
+    <t>C191023</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>BAT60JFILM</t>
+  </si>
+  <si>
+    <t>D16</t>
+  </si>
+  <si>
+    <t>ST(意法半导体)</t>
+  </si>
+  <si>
+    <t>C133103</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>PZ254V-11-04P</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>HDR-TH_4P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>XFCN(兴飞)</t>
+  </si>
+  <si>
+    <t>C492403</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>B-2100S02P-A110</t>
   </si>
   <si>
-    <t>BATT1</t>
-  </si>
-  <si>
-    <t>HDR-TH_2P-P2.54-V-M-1</t>
+    <t>H2,SPKR</t>
+  </si>
+  <si>
+    <t>SMT wire pad (2)</t>
   </si>
   <si>
     <t>Ckmtw(灿科盟)</t>
@@ -106,472 +343,331 @@
     <t>C124375</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>C56</t>
-  </si>
-  <si>
-    <t>C1206</t>
-  </si>
-  <si>
-    <t>CL31A107MQHNNNE</t>
-  </si>
-  <si>
-    <t>SAMSUNG(三星)</t>
-  </si>
-  <si>
-    <t>C15008</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10pF</t>
-  </si>
-  <si>
-    <t>C57</t>
-  </si>
-  <si>
-    <t>C0402</t>
-  </si>
-  <si>
-    <t>CL05C100JB5NNNC</t>
-  </si>
-  <si>
-    <t>C32949</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>C58</t>
-  </si>
-  <si>
-    <t>C0805</t>
-  </si>
-  <si>
-    <t>CL21A226MAQNNNE</t>
-  </si>
-  <si>
-    <t>C45783</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>47uF</t>
-  </si>
-  <si>
-    <t>C66,C67,C133,C134,C135,C136,C137</t>
-  </si>
-  <si>
-    <t>CL21A476MQYNNNE</t>
-  </si>
-  <si>
-    <t>C16780</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>220pF</t>
-  </si>
-  <si>
-    <t>C70,C71</t>
-  </si>
-  <si>
-    <t>0402B221K500NT</t>
-  </si>
-  <si>
-    <t>FH(风华)</t>
-  </si>
-  <si>
-    <t>C1530</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C74,C80</t>
-  </si>
-  <si>
-    <t>CL05A106MQ5NUNC</t>
-  </si>
-  <si>
-    <t>C15525</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C77,C115,C116,C121,C122,C123,C130,C131</t>
-  </si>
-  <si>
-    <t>CL05A105KA5NQNC</t>
-  </si>
-  <si>
-    <t>C52923</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>C81,C82</t>
-  </si>
-  <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>CL10A106MA8NRNC</t>
-  </si>
-  <si>
-    <t>C96446</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>2.2uF</t>
-  </si>
-  <si>
-    <t>C83</t>
-  </si>
-  <si>
-    <t>CL10A225KO8NNNC</t>
-  </si>
-  <si>
-    <t>C23630</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>19</t>
+  </si>
+  <si>
+    <t>B3U-3000PM-B</t>
+  </si>
+  <si>
+    <t>HOME,VOL_DOWN,VOL_UP</t>
+  </si>
+  <si>
+    <t>KEY-SMD_B3U-3000PM-B</t>
+  </si>
+  <si>
+    <t>OMRON(欧姆龙)</t>
+  </si>
+  <si>
+    <t>C306884</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>RCKid2 Cartridge Connector Riser</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>RCKID CARTRIDGE PCB RISER</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>HDR-M-2.54_1x4</t>
+  </si>
+  <si>
+    <t>J5,J7,J8,USB1</t>
+  </si>
+  <si>
+    <t>HDR-M-2.54_1X4</t>
+  </si>
+  <si>
+    <t>C124378</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>GZ1608D601TF</t>
+  </si>
+  <si>
+    <t>L9,L10</t>
+  </si>
+  <si>
+    <t>L0603</t>
+  </si>
+  <si>
+    <t>600Ω</t>
+  </si>
+  <si>
+    <t>Sunlord(顺络)</t>
+  </si>
+  <si>
+    <t>C1002</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>1uH</t>
+  </si>
+  <si>
+    <t>L13</t>
+  </si>
+  <si>
+    <t>IND-SMD_L3.0-W3.0_NR3010</t>
+  </si>
+  <si>
+    <t>NR3015T1R0N</t>
+  </si>
+  <si>
+    <t>TAIYO YUDEN(太诱)</t>
+  </si>
+  <si>
+    <t>C92931</t>
+  </si>
+  <si>
+    <t>XL-1615RGBC-WS2812B</t>
+  </si>
+  <si>
+    <t>LED7,LED8,LED9,LED10,LED11,LED12</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L1.6-W1.5_XL-1615RGBC-WS2812B</t>
+  </si>
+  <si>
+    <t>XINGLIGHT(成兴光)</t>
+  </si>
+  <si>
+    <t>C5349954</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C92,C95,C96,C97,C98,C100,C101,C102,C103,C104,C107,C108,C109,C110,C111,C112,C113,C114,C117,C118,C119,C124,C125,C126,C129</t>
-  </si>
-  <si>
-    <t>CL05B104KB54PNC</t>
-  </si>
-  <si>
-    <t>C307331</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>33pF</t>
-  </si>
-  <si>
-    <t>C105,C106</t>
-  </si>
-  <si>
-    <t>0402CG330J500NT</t>
-  </si>
-  <si>
-    <t>C1562</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>C132</t>
-  </si>
-  <si>
-    <t>CL10A226MQ8NRNC</t>
-  </si>
-  <si>
-    <t>C59461</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>C138</t>
-  </si>
-  <si>
-    <t>CL05A475MP5NRNC</t>
-  </si>
-  <si>
-    <t>C23733</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>B3U-3000P</t>
-  </si>
-  <si>
-    <t>CART_IN1,HOME1,VOL_DOWN1,VOL_UP1</t>
-  </si>
-  <si>
-    <t>KEY-SMD_B3U-3000P</t>
-  </si>
-  <si>
-    <t>OMRON(欧姆龙)</t>
-  </si>
-  <si>
-    <t>C963349</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>B5819WSL</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>SOD-123_L2.7-W1.6-LS3.7-RD-1</t>
-  </si>
-  <si>
-    <t>CJ(江苏长电/长晶)</t>
-  </si>
-  <si>
-    <t>C8598</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>1N5819WS</t>
-  </si>
-  <si>
-    <t>D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16</t>
-  </si>
-  <si>
-    <t>SOD-323_L1.8-W1.3-LS2.5-RD</t>
-  </si>
-  <si>
-    <t>Hottech(合科泰)</t>
-  </si>
-  <si>
-    <t>C191023</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>HDR-TH_4P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>SMT wire pad (2)</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>RCKid2 Cartridge Connector Riser</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>RCKID CARTRIDGE PCB RISER</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>HDR-M-2.54_1x4</t>
-  </si>
-  <si>
-    <t>J5,J7,J8,J9,J10,J11,J12,USB1</t>
-  </si>
-  <si>
-    <t>HDR-M-2.54_1X4</t>
-  </si>
-  <si>
-    <t>C124378</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>1.5uH</t>
-  </si>
-  <si>
-    <t>L7</t>
-  </si>
-  <si>
-    <t>IND-SMD_L2.5-W2.0</t>
-  </si>
-  <si>
-    <t>GCDA252012P-1R5MC</t>
-  </si>
-  <si>
-    <t>GLE(格莱尔)</t>
-  </si>
-  <si>
-    <t>C439319</t>
-  </si>
-  <si>
-    <t>GZ1608D601TF</t>
-  </si>
-  <si>
-    <t>L9,L10</t>
-  </si>
-  <si>
-    <t>L0603</t>
-  </si>
-  <si>
-    <t>Sunlord(顺络)</t>
-  </si>
-  <si>
-    <t>C1002</t>
+    <t>AO3400A</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.6-P1.90-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>AOS</t>
+  </si>
+  <si>
+    <t>C20917</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>WS2812E-MINI-X1</t>
-  </si>
-  <si>
-    <t>LED1,LED2,LED3,LED4</t>
-  </si>
-  <si>
-    <t>LED-SMD_4P-L3.7-W3.5-P1.75-BR-SK6812MINI</t>
-  </si>
-  <si>
-    <t>worldsemi</t>
-  </si>
-  <si>
-    <t>C4154871</t>
+    <t>AO3401A</t>
+  </si>
+  <si>
+    <t>Q7,Q8</t>
+  </si>
+  <si>
+    <t>SOT-23_L2.9-W1.3-P1.90-LS2.4-BR</t>
+  </si>
+  <si>
+    <t>C15127</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>AO3400A</t>
-  </si>
-  <si>
-    <t>Q4,Q6</t>
-  </si>
-  <si>
-    <t>SOT-23-3_L2.9-W1.6-P1.90-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>AOS</t>
-  </si>
-  <si>
-    <t>C20917</t>
+    <t>100Ω</t>
+  </si>
+  <si>
+    <t>R31,R32,R37,R38</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>0402WGF1000TCE</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>C25076</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>AO3401A</t>
-  </si>
-  <si>
-    <t>Q7,Q8</t>
-  </si>
-  <si>
-    <t>SOT-23_L2.9-W1.3-P1.90-LS2.4-BR</t>
-  </si>
-  <si>
-    <t>C15127</t>
+    <t>2.2kΩ</t>
+  </si>
+  <si>
+    <t>R45,R46,R86</t>
+  </si>
+  <si>
+    <t>0402WGF2201TCE</t>
+  </si>
+  <si>
+    <t>C25879</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>1.5kΩ</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>0402WGF1501TCE</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>C25867</t>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>R48,R52,R53,R54,R55,R56,R67,R73,R74,R76,R83</t>
+  </si>
+  <si>
+    <t>0402WGF1002TCE</t>
+  </si>
+  <si>
+    <t>C25744</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>68kΩ</t>
-  </si>
-  <si>
-    <t>R18</t>
-  </si>
-  <si>
-    <t>0402WGF6802TCE</t>
-  </si>
-  <si>
-    <t>C36871</t>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>R49</t>
+  </si>
+  <si>
+    <t>0402WGF1001TCE</t>
+  </si>
+  <si>
+    <t>C11702</t>
   </si>
   <si>
     <t>31</t>
   </si>
   <si>
-    <t>100kΩ</t>
-  </si>
-  <si>
-    <t>R19,R41,R44</t>
-  </si>
-  <si>
-    <t>0402WGF1003TCE</t>
-  </si>
-  <si>
-    <t>C25741</t>
+    <t>22Ω</t>
+  </si>
+  <si>
+    <t>R50,R51,R77,R78,R79,R80</t>
+  </si>
+  <si>
+    <t>0402WGF220JTCE</t>
+  </si>
+  <si>
+    <t>C25092</t>
   </si>
   <si>
     <t>32</t>
   </si>
   <si>
-    <t>100Ω</t>
-  </si>
-  <si>
-    <t>R29,R30,R31,R32,R33,R34,R37,R38</t>
-  </si>
-  <si>
-    <t>0402WGF1000TCE</t>
-  </si>
-  <si>
-    <t>C25076</t>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>R57,R58</t>
+  </si>
+  <si>
+    <t>0402WGF5101TCE</t>
+  </si>
+  <si>
+    <t>C25905</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
+    <t>1Ω</t>
+  </si>
+  <si>
+    <t>R65</t>
+  </si>
+  <si>
+    <t>R0805</t>
+  </si>
+  <si>
+    <t>0805W8F100KT5E</t>
+  </si>
+  <si>
+    <t>C25271</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>220Ω</t>
+  </si>
+  <si>
+    <t>R69,R70</t>
+  </si>
+  <si>
+    <t>0402WGF2200TCE</t>
+  </si>
+  <si>
+    <t>C25091</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>1.8kΩ</t>
+  </si>
+  <si>
+    <t>R71,R72</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>0603WAF1801T5E</t>
+  </si>
+  <si>
+    <t>C4177</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>10mΩ</t>
+  </si>
+  <si>
+    <t>R81</t>
+  </si>
+  <si>
+    <t>RTT05R010FTP</t>
+  </si>
+  <si>
+    <t>RALEC(旺诠)</t>
+  </si>
+  <si>
+    <t>C104574</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>5.11Ω</t>
+  </si>
+  <si>
+    <t>R84</t>
+  </si>
+  <si>
+    <t>WR04W5R11FTL</t>
+  </si>
+  <si>
+    <t>Walsin(华新科)</t>
+  </si>
+  <si>
+    <t>C396142</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
     <t>470Ω</t>
   </si>
   <si>
-    <t>R35,R36</t>
+    <t>R87,R88</t>
   </si>
   <si>
     <t>0402WGF4700TCE</t>
@@ -580,457 +676,298 @@
     <t>C25117</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>390kΩ</t>
-  </si>
-  <si>
-    <t>R43</t>
-  </si>
-  <si>
-    <t>0402WGF3903TCE</t>
-  </si>
-  <si>
-    <t>C25782</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>2.2kΩ</t>
-  </si>
-  <si>
-    <t>R45,R46</t>
-  </si>
-  <si>
-    <t>0402WGF2201TCE</t>
-  </si>
-  <si>
-    <t>C25879</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>R47,R48,R52,R53,R54,R55,R56,R67</t>
-  </si>
-  <si>
-    <t>0402WGF1002TCE</t>
-  </si>
-  <si>
-    <t>C25744</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>R49</t>
-  </si>
-  <si>
-    <t>0402WGF1001TCE</t>
-  </si>
-  <si>
-    <t>C11702</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>22Ω</t>
-  </si>
-  <si>
-    <t>R50,R51</t>
-  </si>
-  <si>
-    <t>0402WGF220JTCE</t>
-  </si>
-  <si>
-    <t>C25092</t>
-  </si>
-  <si>
     <t>39</t>
   </si>
   <si>
-    <t>5.1kΩ</t>
-  </si>
-  <si>
-    <t>R57,R58,R59,R60,R61,R62,R63,R64</t>
-  </si>
-  <si>
-    <t>0402WGF5101TCE</t>
-  </si>
-  <si>
-    <t>C25905</t>
+    <t>DM3CS-SF</t>
+  </si>
+  <si>
+    <t>TF1</t>
+  </si>
+  <si>
+    <t>TF-SMD_DM3CS-SF</t>
+  </si>
+  <si>
+    <t>HRS(广濑)</t>
+  </si>
+  <si>
+    <t>C202111</t>
   </si>
   <si>
     <t>40</t>
   </si>
   <si>
-    <t>1Ω</t>
-  </si>
-  <si>
-    <t>R65</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>0805W8F100KT5E</t>
-  </si>
-  <si>
-    <t>C25271</t>
+    <t>SRV05-4-P-T7</t>
+  </si>
+  <si>
+    <t>TV4</t>
+  </si>
+  <si>
+    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>PROTEK</t>
+  </si>
+  <si>
+    <t>C85364</t>
   </si>
   <si>
     <t>41</t>
   </si>
   <si>
-    <t>2.2Ω</t>
-  </si>
-  <si>
-    <t>R68</t>
-  </si>
-  <si>
-    <t>0805W8F220KT5E</t>
-  </si>
-  <si>
-    <t>C17521</t>
+    <t>INA219AIDCNR</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>SOT-23-8_L3.0-W1.7-P0.65-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>TI(德州仪器)</t>
+  </si>
+  <si>
+    <t>C87469</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>HDC1080DMBR</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>SENSOR-SMD_HDC1080DMBR</t>
-  </si>
-  <si>
-    <t>TI(德州仪器)</t>
-  </si>
-  <si>
-    <t>C82227</t>
+    <t>WMM7040DTHN0-8/TR</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>QFN-8_L4.0-W3.0_WMM7040DTHN0-8-TR</t>
+  </si>
+  <si>
+    <t>C9900000758</t>
   </si>
   <si>
     <t>43</t>
   </si>
   <si>
-    <t>TS-1187A-B-A-B</t>
-  </si>
-  <si>
-    <t>SELECT1,START1</t>
-  </si>
-  <si>
-    <t>SW-SMD_4P-L5.1-W5.1-P3.70-LS6.5-TL-2</t>
-  </si>
-  <si>
-    <t>XKB Connectivity(中国星坤)</t>
-  </si>
-  <si>
-    <t>C318884</t>
+    <t>ST7789V 2.8&amp;quot; IPS 320x240 37P 8080 8bit</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>ST7789V 2.8\" IPS DISPLAY 320X240 37P</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>HDR-M-2.54_1x2</t>
-  </si>
-  <si>
-    <t>SPKR1</t>
-  </si>
-  <si>
-    <t>HDR-M-2.54_1X2</t>
+    <t>RCKid2 Cartridge Connector Female</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>RCKid Cartridge Riser</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>DM3CS-SF</t>
-  </si>
-  <si>
-    <t>TF1</t>
-  </si>
-  <si>
-    <t>TF-SMD_DM3CS-SF</t>
-  </si>
-  <si>
-    <t>HRS(广濑)</t>
-  </si>
-  <si>
-    <t>C202111</t>
+    <t>SN74LVC2G17DBVR</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
+    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>C10429</t>
   </si>
   <si>
     <t>46</t>
   </si>
   <si>
-    <t>SRV05-4-P-T7</t>
-  </si>
-  <si>
-    <t>TV4,TV5,TV6,TV7</t>
-  </si>
-  <si>
-    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>PROTEK</t>
-  </si>
-  <si>
-    <t>C85364</t>
+    <t>PAM8302AASCR</t>
+  </si>
+  <si>
+    <t>U20</t>
+  </si>
+  <si>
+    <t>MSOP-8_L3.0-W3.0-P0.65-LS5.0-BL</t>
+  </si>
+  <si>
+    <t>DIODES(美台)</t>
+  </si>
+  <si>
+    <t>C113367</t>
   </si>
   <si>
     <t>47</t>
   </si>
   <si>
-    <t>WMM7040DTHN0-8/TR</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>QFN-8_L4.0-W3.0_WMM7040DTHN0-8-TR</t>
-  </si>
-  <si>
-    <t>C9900000758</t>
+    <t>TPS7A2030PDBVR</t>
+  </si>
+  <si>
+    <t>U22</t>
+  </si>
+  <si>
+    <t>TSOT-23-5_L2.9-W1.6-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>C963429</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
-    <t>ST7789V 2.8&amp;quot; IPS 320x240 37P 8080 8bit</t>
-  </si>
-  <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>ST7789V 2.8\" IPS DISPLAY 320X240 37P</t>
+    <t>HX4002-MFC</t>
+  </si>
+  <si>
+    <t>U23</t>
+  </si>
+  <si>
+    <t>HEXIN(禾芯微)</t>
+  </si>
+  <si>
+    <t>C172354</t>
   </si>
   <si>
     <t>49</t>
   </si>
   <si>
-    <t>RCKid2 Cartridge Connector Female</t>
-  </si>
-  <si>
-    <t>U14</t>
-  </si>
-  <si>
-    <t>RCKid Cartridge Riser</t>
+    <t>BMI160</t>
+  </si>
+  <si>
+    <t>U26</t>
+  </si>
+  <si>
+    <t>LGA-14_L3.0-W2.5-P0.50-BL</t>
+  </si>
+  <si>
+    <t>Bosch(博世)</t>
+  </si>
+  <si>
+    <t>C94021</t>
   </si>
   <si>
     <t>50</t>
   </si>
   <si>
-    <t>TP4054-42-SOT25R</t>
-  </si>
-  <si>
-    <t>U16</t>
-  </si>
-  <si>
-    <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>TOPPOWER(南京拓微)</t>
-  </si>
-  <si>
-    <t>C32574</t>
+    <t>LTR-390UV-01</t>
+  </si>
+  <si>
+    <t>U28</t>
+  </si>
+  <si>
+    <t>SENSOR-SMD_LTR-390UV-01</t>
+  </si>
+  <si>
+    <t>LITEON(光宝)</t>
+  </si>
+  <si>
+    <t>C492374</t>
   </si>
   <si>
     <t>51</t>
   </si>
   <si>
-    <t>TPS63060DSCR</t>
-  </si>
-  <si>
-    <t>U17</t>
-  </si>
-  <si>
-    <t>WSON-10_L3.0-W3.0-P0.50-BL-EP</t>
-  </si>
-  <si>
-    <t>C48567</t>
+    <t>{ManufacturerPart!}</t>
+  </si>
+  <si>
+    <t>U29</t>
+  </si>
+  <si>
+    <t>LQFN-56_L7.0-W7.0-P0.4-EP</t>
+  </si>
+  <si>
+    <t>RP2040</t>
+  </si>
+  <si>
+    <t>RaspberryPi(树莓派)</t>
+  </si>
+  <si>
+    <t>C2040</t>
   </si>
   <si>
     <t>52</t>
   </si>
   <si>
-    <t>SN74LVC2G17DBVR</t>
-  </si>
-  <si>
-    <t>U19</t>
-  </si>
-  <si>
-    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>C10429</t>
+    <t>ATTINY3217-MFR</t>
+  </si>
+  <si>
+    <t>U31</t>
+  </si>
+  <si>
+    <t>WQFN-24_L4.0-W4.0-P0.50-TL-EP2.6</t>
+  </si>
+  <si>
+    <t>MICROCHIP(美国微芯)</t>
+  </si>
+  <si>
+    <t>C617969</t>
   </si>
   <si>
     <t>53</t>
   </si>
   <si>
-    <t>PAM8302AASCR</t>
-  </si>
-  <si>
-    <t>U20</t>
-  </si>
-  <si>
-    <t>MSOP-8_L3.0-W3.0-P0.65-LS5.0-BL</t>
-  </si>
-  <si>
-    <t>DIODES(美台)</t>
-  </si>
-  <si>
-    <t>C113367</t>
+    <t>MCP73832T-2ACI/OT</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>C38066</t>
   </si>
   <si>
     <t>54</t>
   </si>
   <si>
-    <t>TPS7A2030PDBVR</t>
-  </si>
-  <si>
-    <t>U22</t>
-  </si>
-  <si>
-    <t>TSOT-23-5_L2.9-W1.6-P0.95-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>C963429</t>
+    <t>SN74LVC1T45DBVR</t>
+  </si>
+  <si>
+    <t>U33</t>
+  </si>
+  <si>
+    <t>C7843</t>
   </si>
   <si>
     <t>55</t>
   </si>
   <si>
-    <t>HX4002-MFC</t>
-  </si>
-  <si>
-    <t>U23</t>
-  </si>
-  <si>
-    <t>HEXIN(禾芯微)</t>
-  </si>
-  <si>
-    <t>C172354</t>
+    <t>TPS63001DRCR</t>
+  </si>
+  <si>
+    <t>U34</t>
+  </si>
+  <si>
+    <t>VSON-10_L3.0-W3.0-P0.50-TL-EP_TPS62410DRCR</t>
+  </si>
+  <si>
+    <t>C28060</t>
   </si>
   <si>
     <t>56</t>
   </si>
   <si>
-    <t>BMI160</t>
-  </si>
-  <si>
-    <t>U26</t>
-  </si>
-  <si>
-    <t>LGA-14_L3.0-W2.5-P0.50-BL</t>
-  </si>
-  <si>
-    <t>Bosch(博世)</t>
-  </si>
-  <si>
-    <t>C94021</t>
+    <t>MC-107DM</t>
+  </si>
+  <si>
+    <t>USB4</t>
+  </si>
+  <si>
+    <t>USB-C-SMD_MC-107D</t>
+  </si>
+  <si>
+    <t>HANBO(汉博)</t>
+  </si>
+  <si>
+    <t>C2874569</t>
   </si>
   <si>
     <t>57</t>
-  </si>
-  <si>
-    <t>BMM150</t>
-  </si>
-  <si>
-    <t>U27</t>
-  </si>
-  <si>
-    <t>WLCSP-12_L1.6-W1.6_BMM150</t>
-  </si>
-  <si>
-    <t>C171681</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>LTR-390UV-01</t>
-  </si>
-  <si>
-    <t>U28</t>
-  </si>
-  <si>
-    <t>SENSOR-SMD_LTR-390UV-01</t>
-  </si>
-  <si>
-    <t>LITEON(光宝)</t>
-  </si>
-  <si>
-    <t>C492374</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>{ManufacturerPart!}</t>
-  </si>
-  <si>
-    <t>U29</t>
-  </si>
-  <si>
-    <t>LQFN-56_L7.0-W7.0-P0.4-EP</t>
-  </si>
-  <si>
-    <t>RP2040</t>
-  </si>
-  <si>
-    <t>RaspberryPi(树莓派)</t>
-  </si>
-  <si>
-    <t>C2040</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>U30</t>
-  </si>
-  <si>
-    <t>QFN-20_L3.0-W3.0-P0.40-BL-EP1.7</t>
-  </si>
-  <si>
-    <t>ATTINY1616-MNR</t>
-  </si>
-  <si>
-    <t>MICROCHIP(美国微芯)</t>
-  </si>
-  <si>
-    <t>C507118</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>MC-107DM</t>
-  </si>
-  <si>
-    <t>USB4,USB5,USB6,USB7</t>
-  </si>
-  <si>
-    <t>USB-C-SMD_MC-107D</t>
-  </si>
-  <si>
-    <t>HANBO(汉博)</t>
-  </si>
-  <si>
-    <t>C2874569</t>
-  </si>
-  <si>
-    <t>62</t>
   </si>
   <si>
     <t>12MHz</t>
@@ -1425,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -1500,7 +1437,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -1532,7 +1469,7 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -1547,45 +1484,45 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -1593,31 +1530,31 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>41</v>
       </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>
@@ -1625,10 +1562,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
@@ -1637,19 +1574,19 @@
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
         <v>44</v>
       </c>
       <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
         <v>47</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
       </c>
       <c r="J7" t="s">
         <v>18</v>
@@ -1657,31 +1594,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
         <v>51</v>
       </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
         <v>52</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" t="s">
-        <v>53</v>
       </c>
       <c r="J8" t="s">
         <v>18</v>
@@ -1689,31 +1626,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
         <v>55</v>
       </c>
-      <c r="D9" t="s">
+      <c r="H9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
         <v>56</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" t="s">
-        <v>59</v>
       </c>
       <c r="J9" t="s">
         <v>18</v>
@@ -1721,31 +1658,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
         <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" t="s">
-        <v>64</v>
       </c>
       <c r="J10" t="s">
         <v>18</v>
@@ -1753,31 +1690,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
         <v>65</v>
       </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
         <v>66</v>
       </c>
-      <c r="D11" t="s">
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
         <v>67</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" t="s">
-        <v>69</v>
       </c>
       <c r="J11" t="s">
         <v>18</v>
@@ -1785,31 +1722,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
         <v>71</v>
       </c>
-      <c r="E12" t="s">
+      <c r="H12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" t="s">
         <v>72</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" t="s">
-        <v>74</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -1817,31 +1754,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
         <v>75</v>
       </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s">
         <v>76</v>
       </c>
-      <c r="D13" t="s">
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" t="s">
         <v>77</v>
-      </c>
-      <c r="E13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" t="s">
-        <v>79</v>
       </c>
       <c r="J13" t="s">
         <v>18</v>
@@ -1849,31 +1786,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
         <v>80</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" t="s">
         <v>81</v>
       </c>
-      <c r="C14" t="s">
+      <c r="H14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" t="s">
         <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" t="s">
-        <v>85</v>
       </c>
       <c r="J14" t="s">
         <v>18</v>
@@ -1881,31 +1818,31 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" t="s">
         <v>86</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" t="s">
-        <v>90</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -1913,31 +1850,31 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" t="s">
         <v>91</v>
       </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="I16" t="s">
         <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" t="s">
-        <v>94</v>
       </c>
       <c r="J16" t="s">
         <v>18</v>
@@ -1945,31 +1882,31 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" t="s">
         <v>96</v>
       </c>
-      <c r="D17" t="s">
+      <c r="I17" t="s">
         <v>97</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" t="s">
-        <v>99</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
@@ -1977,31 +1914,31 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
         <v>100</v>
       </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>101</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" t="s">
         <v>102</v>
       </c>
-      <c r="E18" t="s">
+      <c r="I18" t="s">
         <v>103</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" t="s">
-        <v>105</v>
       </c>
       <c r="J18" t="s">
         <v>18</v>
@@ -2009,31 +1946,31 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
         <v>106</v>
       </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>107</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" t="s">
         <v>108</v>
       </c>
-      <c r="E19" t="s">
+      <c r="I19" t="s">
         <v>109</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" t="s">
-        <v>110</v>
-      </c>
-      <c r="I19" t="s">
-        <v>111</v>
       </c>
       <c r="J19" t="s">
         <v>18</v>
@@ -2041,31 +1978,31 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" t="s">
         <v>112</v>
       </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>113</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" t="s">
         <v>114</v>
       </c>
-      <c r="E20" t="s">
+      <c r="I20" t="s">
         <v>115</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>113</v>
-      </c>
-      <c r="H20" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" t="s">
-        <v>117</v>
       </c>
       <c r="J20" t="s">
         <v>18</v>
@@ -2073,19 +2010,19 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" t="s">
         <v>119</v>
-      </c>
-      <c r="E21" t="s">
-        <v>120</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
@@ -2105,13 +2042,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
         <v>121</v>
-      </c>
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" t="s">
-        <v>26</v>
       </c>
       <c r="D22" t="s">
         <v>122</v>
@@ -2123,13 +2060,13 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="J22" t="s">
         <v>18</v>
@@ -2137,63 +2074,63 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" t="s">
         <v>126</v>
       </c>
-      <c r="E23" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
       <c r="H23" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="H24" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="I24" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J24" t="s">
         <v>18</v>
@@ -2201,31 +2138,31 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F25" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H25" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I25" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J25" t="s">
         <v>18</v>
@@ -2233,31 +2170,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H26" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I26" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J26" t="s">
         <v>18</v>
@@ -2265,31 +2202,31 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E27" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" t="s">
         <v>148</v>
       </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" t="s">
-        <v>146</v>
-      </c>
-      <c r="H27" t="s">
-        <v>149</v>
-      </c>
       <c r="I27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J27" t="s">
         <v>18</v>
@@ -2297,31 +2234,31 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E28" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="G28" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H28" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J28" t="s">
         <v>18</v>
@@ -2329,31 +2266,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" t="s">
+        <v>164</v>
+      </c>
+      <c r="E29" t="s">
         <v>158</v>
       </c>
-      <c r="D29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" t="s">
         <v>160</v>
       </c>
-      <c r="F29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" t="s">
-        <v>158</v>
-      </c>
-      <c r="H29" t="s">
-        <v>155</v>
-      </c>
       <c r="I29" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J29" t="s">
         <v>18</v>
@@ -2361,31 +2298,31 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D30" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E30" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F30" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G30" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H30" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I30" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
@@ -2393,31 +2330,31 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D31" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E31" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H31" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I31" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J31" t="s">
         <v>18</v>
@@ -2425,31 +2362,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E32" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F32" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G32" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H32" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I32" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J32" t="s">
         <v>18</v>
@@ -2457,31 +2394,31 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G33" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H33" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J33" t="s">
         <v>18</v>
@@ -2489,31 +2426,31 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="F34" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G34" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H34" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I34" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J34" t="s">
         <v>18</v>
@@ -2521,31 +2458,31 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D35" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E35" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F35" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G35" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H35" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I35" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J35" t="s">
         <v>18</v>
@@ -2553,31 +2490,31 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s">
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D36" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E36" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="F36" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G36" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H36" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I36" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J36" t="s">
         <v>18</v>
@@ -2585,31 +2522,31 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D37" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E37" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="F37" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G37" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H37" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="I37" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J37" t="s">
         <v>18</v>
@@ -2617,31 +2554,31 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D38" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E38" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F38" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="G38" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H38" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="I38" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="J38" t="s">
         <v>18</v>
@@ -2649,31 +2586,31 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B39" t="s">
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D39" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E39" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F39" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G39" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H39" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I39" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="J39" t="s">
         <v>18</v>
@@ -2681,31 +2618,31 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D40" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E40" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="F40" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H40" t="s">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="I40" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J40" t="s">
         <v>18</v>
@@ -2713,31 +2650,31 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D41" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F41" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H41" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="I41" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="J41" t="s">
         <v>18</v>
@@ -2745,31 +2682,31 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D42" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E42" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F42" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H42" t="s">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="I42" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="J42" t="s">
         <v>18</v>
@@ -2777,31 +2714,31 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E43" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="H43" t="s">
-        <v>234</v>
+        <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="J43" t="s">
         <v>18</v>
@@ -2809,51 +2746,51 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D44" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E44" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>240</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>241</v>
+        <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D45" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E45" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -2865,39 +2802,39 @@
         <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D46" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E46" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="H46" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="I46" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J46" t="s">
         <v>18</v>
@@ -2905,31 +2842,31 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D47" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E47" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F47" t="s">
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H47" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I47" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="J47" t="s">
         <v>18</v>
@@ -2937,31 +2874,31 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E48" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F48" t="s">
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H48" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="I48" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="J48" t="s">
         <v>18</v>
@@ -2969,95 +2906,95 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D49" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E49" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="F49" t="s">
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>269</v>
       </c>
       <c r="H49" t="s">
-        <v>15</v>
+        <v>271</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="J49" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D50" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E50" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F50" t="s">
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>274</v>
       </c>
       <c r="H50" t="s">
-        <v>15</v>
+        <v>277</v>
       </c>
       <c r="I50" t="s">
-        <v>15</v>
+        <v>278</v>
       </c>
       <c r="J50" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D51" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="E51" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F51" t="s">
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="H51" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="I51" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="J51" t="s">
         <v>18</v>
@@ -3065,31 +3002,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D52" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E52" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F52" t="s">
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="H52" t="s">
-        <v>234</v>
+        <v>290</v>
       </c>
       <c r="I52" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="J52" t="s">
         <v>18</v>
@@ -3097,31 +3034,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D53" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="E53" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="F53" t="s">
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="H53" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="I53" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="J53" t="s">
         <v>18</v>
@@ -3129,31 +3066,31 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="D54" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E54" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="F54" t="s">
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="H54" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I54" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="J54" t="s">
         <v>18</v>
@@ -3161,31 +3098,31 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D55" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="E55" t="s">
-        <v>296</v>
+        <v>230</v>
       </c>
       <c r="F55" t="s">
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="H55" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I55" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="J55" t="s">
         <v>18</v>
@@ -3193,31 +3130,31 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D56" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E56" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="F56" t="s">
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="H56" t="s">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="I56" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="J56" t="s">
         <v>18</v>
@@ -3225,31 +3162,31 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D57" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="E57" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F57" t="s">
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="H57" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="I57" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="J57" t="s">
         <v>18</v>
@@ -3257,198 +3194,38 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D58" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="E58" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>319</v>
       </c>
       <c r="G58" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="H58" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="I58" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="J58" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>314</v>
-      </c>
-      <c r="B59" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" t="s">
-        <v>315</v>
-      </c>
-      <c r="D59" t="s">
-        <v>316</v>
-      </c>
-      <c r="E59" t="s">
-        <v>317</v>
-      </c>
-      <c r="F59" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59" t="s">
-        <v>315</v>
-      </c>
-      <c r="H59" t="s">
-        <v>318</v>
-      </c>
-      <c r="I59" t="s">
-        <v>319</v>
-      </c>
-      <c r="J59" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>320</v>
-      </c>
-      <c r="B60" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" t="s">
-        <v>321</v>
-      </c>
-      <c r="D60" t="s">
-        <v>322</v>
-      </c>
-      <c r="E60" t="s">
-        <v>323</v>
-      </c>
-      <c r="F60" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60" t="s">
-        <v>324</v>
-      </c>
-      <c r="H60" t="s">
-        <v>325</v>
-      </c>
-      <c r="I60" t="s">
-        <v>326</v>
-      </c>
-      <c r="J60" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>327</v>
-      </c>
-      <c r="B61" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>321</v>
-      </c>
-      <c r="D61" t="s">
-        <v>328</v>
-      </c>
-      <c r="E61" t="s">
-        <v>329</v>
-      </c>
-      <c r="F61" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" t="s">
-        <v>330</v>
-      </c>
-      <c r="H61" t="s">
-        <v>331</v>
-      </c>
-      <c r="I61" t="s">
-        <v>332</v>
-      </c>
-      <c r="J61" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>333</v>
-      </c>
-      <c r="B62" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" t="s">
-        <v>334</v>
-      </c>
-      <c r="D62" t="s">
-        <v>335</v>
-      </c>
-      <c r="E62" t="s">
-        <v>336</v>
-      </c>
-      <c r="F62" t="s">
-        <v>15</v>
-      </c>
-      <c r="G62" t="s">
-        <v>334</v>
-      </c>
-      <c r="H62" t="s">
-        <v>337</v>
-      </c>
-      <c r="I62" t="s">
-        <v>338</v>
-      </c>
-      <c r="J62" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>339</v>
-      </c>
-      <c r="B63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" t="s">
-        <v>340</v>
-      </c>
-      <c r="D63" t="s">
-        <v>341</v>
-      </c>
-      <c r="E63" t="s">
-        <v>342</v>
-      </c>
-      <c r="F63" t="s">
-        <v>340</v>
-      </c>
-      <c r="G63" t="s">
-        <v>343</v>
-      </c>
-      <c r="H63" t="s">
-        <v>344</v>
-      </c>
-      <c r="I63" t="s">
-        <v>345</v>
-      </c>
-      <c r="J63" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
         <v>15</v>
       </c>
     </row>

--- a/hardware/RCKid2-bom.xlsx
+++ b/hardware/RCKid2-bom.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_RCKid_RCKid_2024-03-09" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_RCKid_RCKid_2024-06-25" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="330">
   <si>
     <t>No.</t>
   </si>
@@ -97,7 +97,7 @@
     <t>B+,B-</t>
   </si>
   <si>
-    <t>HDR-TH_1P-V-M_XKB_X4611WV-01I-C28D40</t>
+    <t>hdr-th_1p-v-m_xkb_x4611wv-01i-c28d40</t>
   </si>
   <si>
     <t>4</t>
@@ -316,7 +316,7 @@
     <t>H1</t>
   </si>
   <si>
-    <t>HDR-TH_4P-P2.54-V-M</t>
+    <t>hdr-th_4p-p2.54-v-m</t>
   </si>
   <si>
     <t>XFCN(兴飞)</t>
@@ -352,7 +352,7 @@
     <t>HOME,VOL_DOWN,VOL_UP</t>
   </si>
   <si>
-    <t>KEY-SMD_B3U-3000PM-B</t>
+    <t>key-smd_b3u-3000pm-b</t>
   </si>
   <si>
     <t>OMRON(欧姆龙)</t>
@@ -382,7 +382,7 @@
     <t>J5,J7,J8,USB1</t>
   </si>
   <si>
-    <t>HDR-M-2.54_1X4</t>
+    <t>hdr-m-2.54_1x4</t>
   </si>
   <si>
     <t>C124378</t>
@@ -451,7 +451,7 @@
     <t>AO3400A</t>
   </si>
   <si>
-    <t>Q6</t>
+    <t>Q6,Q9</t>
   </si>
   <si>
     <t>SOT-23-3_L2.9-W1.6-P1.90-LS2.8-BR</t>
@@ -469,7 +469,7 @@
     <t>AO3401A</t>
   </si>
   <si>
-    <t>Q7,Q8</t>
+    <t>Q8</t>
   </si>
   <si>
     <t>SOT-23_L2.9-W1.3-P1.90-LS2.4-BR</t>
@@ -520,7 +520,7 @@
     <t>10kΩ</t>
   </si>
   <si>
-    <t>R48,R52,R53,R54,R55,R56,R67,R73,R74,R76,R83</t>
+    <t>R48,R52,R54,R55,R56,R67,R73,R74,R76,R83</t>
   </si>
   <si>
     <t>0402WGF1002TCE</t>
@@ -535,7 +535,7 @@
     <t>1kΩ</t>
   </si>
   <si>
-    <t>R49</t>
+    <t>R49,R91,R92</t>
   </si>
   <si>
     <t>0402WGF1001TCE</t>
@@ -679,6 +679,21 @@
     <t>39</t>
   </si>
   <si>
+    <t>4.7kΩ</t>
+  </si>
+  <si>
+    <t>R89,R90</t>
+  </si>
+  <si>
+    <t>0402WGF4701TCE</t>
+  </si>
+  <si>
+    <t>C25900</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>DM3CS-SF</t>
   </si>
   <si>
@@ -694,7 +709,7 @@
     <t>C202111</t>
   </si>
   <si>
-    <t>40</t>
+    <t>41</t>
   </si>
   <si>
     <t>SRV05-4-P-T7</t>
@@ -712,7 +727,7 @@
     <t>C85364</t>
   </si>
   <si>
-    <t>41</t>
+    <t>42</t>
   </si>
   <si>
     <t>INA219AIDCNR</t>
@@ -730,7 +745,7 @@
     <t>C87469</t>
   </si>
   <si>
-    <t>42</t>
+    <t>43</t>
   </si>
   <si>
     <t>WMM7040DTHN0-8/TR</t>
@@ -745,7 +760,7 @@
     <t>C9900000758</t>
   </si>
   <si>
-    <t>43</t>
+    <t>44</t>
   </si>
   <si>
     <t>ST7789V 2.8&amp;quot; IPS 320x240 37P 8080 8bit</t>
@@ -757,19 +772,19 @@
     <t>ST7789V 2.8\" IPS DISPLAY 320X240 37P</t>
   </si>
   <si>
-    <t>44</t>
+    <t>45</t>
   </si>
   <si>
     <t>RCKid2 Cartridge Connector Female</t>
   </si>
   <si>
-    <t>U14</t>
-  </si>
-  <si>
-    <t>RCKid Cartridge Riser</t>
-  </si>
-  <si>
-    <t>45</t>
+    <t>U14,U35</t>
+  </si>
+  <si>
+    <t>rckid cartridge riser</t>
+  </si>
+  <si>
+    <t>46</t>
   </si>
   <si>
     <t>SN74LVC2G17DBVR</t>
@@ -784,7 +799,7 @@
     <t>C10429</t>
   </si>
   <si>
-    <t>46</t>
+    <t>47</t>
   </si>
   <si>
     <t>PAM8302AASCR</t>
@@ -802,7 +817,7 @@
     <t>C113367</t>
   </si>
   <si>
-    <t>47</t>
+    <t>48</t>
   </si>
   <si>
     <t>TPS7A2030PDBVR</t>
@@ -817,7 +832,7 @@
     <t>C963429</t>
   </si>
   <si>
-    <t>48</t>
+    <t>49</t>
   </si>
   <si>
     <t>HX4002-MFC</t>
@@ -832,7 +847,7 @@
     <t>C172354</t>
   </si>
   <si>
-    <t>49</t>
+    <t>50</t>
   </si>
   <si>
     <t>BMI160</t>
@@ -850,7 +865,7 @@
     <t>C94021</t>
   </si>
   <si>
-    <t>50</t>
+    <t>51</t>
   </si>
   <si>
     <t>LTR-390UV-01</t>
@@ -868,7 +883,7 @@
     <t>C492374</t>
   </si>
   <si>
-    <t>51</t>
+    <t>52</t>
   </si>
   <si>
     <t>{ManufacturerPart!}</t>
@@ -889,7 +904,7 @@
     <t>C2040</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t>ATTINY3217-MFR</t>
@@ -907,7 +922,7 @@
     <t>C617969</t>
   </si>
   <si>
-    <t>53</t>
+    <t>54</t>
   </si>
   <si>
     <t>MCP73832T-2ACI/OT</t>
@@ -922,7 +937,7 @@
     <t>C38066</t>
   </si>
   <si>
-    <t>54</t>
+    <t>55</t>
   </si>
   <si>
     <t>SN74LVC1T45DBVR</t>
@@ -934,7 +949,7 @@
     <t>C7843</t>
   </si>
   <si>
-    <t>55</t>
+    <t>56</t>
   </si>
   <si>
     <t>TPS63001DRCR</t>
@@ -949,7 +964,7 @@
     <t>C28060</t>
   </si>
   <si>
-    <t>56</t>
+    <t>57</t>
   </si>
   <si>
     <t>MC-107DM</t>
@@ -967,7 +982,7 @@
     <t>C2874569</t>
   </si>
   <si>
-    <t>57</t>
+    <t>58</t>
   </si>
   <si>
     <t>12MHz</t>
@@ -1362,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -2173,7 +2188,7 @@
         <v>144</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
         <v>145</v>
@@ -2205,7 +2220,7 @@
         <v>150</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
         <v>151</v>
@@ -2301,7 +2316,7 @@
         <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
         <v>168</v>
@@ -2333,7 +2348,7 @@
         <v>172</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
         <v>173</v>
@@ -2621,7 +2636,7 @@
         <v>221</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C40" t="s">
         <v>222</v>
@@ -2630,19 +2645,19 @@
         <v>223</v>
       </c>
       <c r="E40" t="s">
+        <v>158</v>
+      </c>
+      <c r="F40" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" t="s">
         <v>224</v>
       </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" t="s">
-        <v>222</v>
-      </c>
       <c r="H40" t="s">
+        <v>160</v>
+      </c>
+      <c r="I40" t="s">
         <v>225</v>
-      </c>
-      <c r="I40" t="s">
-        <v>226</v>
       </c>
       <c r="J40" t="s">
         <v>18</v>
@@ -2650,31 +2665,31 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41" t="s">
+        <v>227</v>
+      </c>
+      <c r="D41" t="s">
         <v>228</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>229</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s">
+        <v>227</v>
+      </c>
+      <c r="H41" t="s">
         <v>230</v>
       </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" t="s">
-        <v>228</v>
-      </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>231</v>
-      </c>
-      <c r="I41" t="s">
-        <v>232</v>
       </c>
       <c r="J41" t="s">
         <v>18</v>
@@ -2682,31 +2697,31 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D42" t="s">
         <v>234</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>235</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
+        <v>233</v>
+      </c>
+      <c r="H42" t="s">
         <v>236</v>
       </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" t="s">
-        <v>234</v>
-      </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>237</v>
-      </c>
-      <c r="I42" t="s">
-        <v>238</v>
       </c>
       <c r="J42" t="s">
         <v>18</v>
@@ -2714,28 +2729,28 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" t="s">
         <v>240</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>241</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>239</v>
+      </c>
+      <c r="H43" t="s">
         <v>242</v>
-      </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" t="s">
-        <v>240</v>
-      </c>
-      <c r="H43" t="s">
-        <v>15</v>
       </c>
       <c r="I43" t="s">
         <v>243</v>
@@ -2764,33 +2779,33 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>245</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>15</v>
+        <v>248</v>
       </c>
       <c r="J44" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D45" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -2810,34 +2825,34 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E46" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>253</v>
+        <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>256</v>
+        <v>15</v>
       </c>
       <c r="J46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2863,10 +2878,10 @@
         <v>258</v>
       </c>
       <c r="H47" t="s">
+        <v>242</v>
+      </c>
+      <c r="I47" t="s">
         <v>261</v>
-      </c>
-      <c r="I47" t="s">
-        <v>262</v>
       </c>
       <c r="J47" t="s">
         <v>18</v>
@@ -2874,28 +2889,28 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48" t="s">
+        <v>263</v>
+      </c>
+      <c r="D48" t="s">
         <v>264</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>265</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s">
+        <v>263</v>
+      </c>
+      <c r="H48" t="s">
         <v>266</v>
-      </c>
-      <c r="F48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48" t="s">
-        <v>264</v>
-      </c>
-      <c r="H48" t="s">
-        <v>237</v>
       </c>
       <c r="I48" t="s">
         <v>267</v>
@@ -2918,7 +2933,7 @@
         <v>270</v>
       </c>
       <c r="E49" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="F49" t="s">
         <v>15</v>
@@ -2927,7 +2942,7 @@
         <v>269</v>
       </c>
       <c r="H49" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="I49" t="s">
         <v>272</v>
@@ -2950,7 +2965,7 @@
         <v>275</v>
       </c>
       <c r="E50" t="s">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="F50" t="s">
         <v>15</v>
@@ -2959,10 +2974,10 @@
         <v>274</v>
       </c>
       <c r="H50" t="s">
+        <v>276</v>
+      </c>
+      <c r="I50" t="s">
         <v>277</v>
-      </c>
-      <c r="I50" t="s">
-        <v>278</v>
       </c>
       <c r="J50" t="s">
         <v>18</v>
@@ -2970,31 +2985,31 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51" t="s">
+        <v>279</v>
+      </c>
+      <c r="D51" t="s">
         <v>280</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>281</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
+        <v>279</v>
+      </c>
+      <c r="H51" t="s">
         <v>282</v>
       </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" t="s">
-        <v>280</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>283</v>
-      </c>
-      <c r="I51" t="s">
-        <v>284</v>
       </c>
       <c r="J51" t="s">
         <v>18</v>
@@ -3002,31 +3017,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52" t="s">
+        <v>285</v>
+      </c>
+      <c r="D52" t="s">
         <v>286</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>287</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s">
+        <v>285</v>
+      </c>
+      <c r="H52" t="s">
         <v>288</v>
       </c>
-      <c r="F52" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="I52" t="s">
         <v>289</v>
-      </c>
-      <c r="H52" t="s">
-        <v>290</v>
-      </c>
-      <c r="I52" t="s">
-        <v>291</v>
       </c>
       <c r="J52" t="s">
         <v>18</v>
@@ -3034,31 +3049,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53" t="s">
+        <v>291</v>
+      </c>
+      <c r="D53" t="s">
+        <v>292</v>
+      </c>
+      <c r="E53" t="s">
         <v>293</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s">
         <v>294</v>
       </c>
-      <c r="E53" t="s">
+      <c r="H53" t="s">
         <v>295</v>
       </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" t="s">
-        <v>293</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>296</v>
-      </c>
-      <c r="I53" t="s">
-        <v>297</v>
       </c>
       <c r="J53" t="s">
         <v>18</v>
@@ -3066,28 +3081,28 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54" t="s">
+        <v>298</v>
+      </c>
+      <c r="D54" t="s">
         <v>299</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>300</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s">
+        <v>298</v>
+      </c>
+      <c r="H54" t="s">
         <v>301</v>
-      </c>
-      <c r="F54" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54" t="s">
-        <v>299</v>
-      </c>
-      <c r="H54" t="s">
-        <v>296</v>
       </c>
       <c r="I54" t="s">
         <v>302</v>
@@ -3110,7 +3125,7 @@
         <v>305</v>
       </c>
       <c r="E55" t="s">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="F55" t="s">
         <v>15</v>
@@ -3119,10 +3134,10 @@
         <v>304</v>
       </c>
       <c r="H55" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="I55" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J55" t="s">
         <v>18</v>
@@ -3130,28 +3145,28 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D56" t="s">
+        <v>310</v>
+      </c>
+      <c r="E56" t="s">
+        <v>235</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s">
         <v>309</v>
       </c>
-      <c r="E56" t="s">
-        <v>310</v>
-      </c>
-      <c r="F56" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" t="s">
-        <v>308</v>
-      </c>
       <c r="H56" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I56" t="s">
         <v>311</v>
@@ -3183,10 +3198,10 @@
         <v>313</v>
       </c>
       <c r="H57" t="s">
+        <v>242</v>
+      </c>
+      <c r="I57" t="s">
         <v>316</v>
-      </c>
-      <c r="I57" t="s">
-        <v>317</v>
       </c>
       <c r="J57" t="s">
         <v>18</v>
@@ -3194,38 +3209,70 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58" t="s">
+        <v>318</v>
+      </c>
+      <c r="D58" t="s">
         <v>319</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>320</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s">
+        <v>318</v>
+      </c>
+      <c r="H58" t="s">
         <v>321</v>
       </c>
-      <c r="F58" t="s">
-        <v>319</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="I58" t="s">
         <v>322</v>
       </c>
-      <c r="H58" t="s">
+      <c r="J58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>323</v>
       </c>
-      <c r="I58" t="s">
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
         <v>324</v>
       </c>
-      <c r="J58" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="D59" t="s">
+        <v>325</v>
+      </c>
+      <c r="E59" t="s">
+        <v>326</v>
+      </c>
+      <c r="F59" t="s">
+        <v>324</v>
+      </c>
+      <c r="G59" t="s">
+        <v>327</v>
+      </c>
+      <c r="H59" t="s">
+        <v>328</v>
+      </c>
+      <c r="I59" t="s">
+        <v>329</v>
+      </c>
+      <c r="J59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>15</v>
       </c>
     </row>
